--- a/p6/SAR_BOQ_Cost_Mapping.xlsx
+++ b/p6/SAR_BOQ_Cost_Mapping.xlsx
@@ -60437,16 +60437,16 @@
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Budgeted cost of the activity in SAR from the contract payment conditions applied to the BOQ station value</t>
+          <t>Contract cost of the activity in SAR from the payment conditions applied to the BOQ station value (column L of BOQ_Mapping)</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Material resource: cost only. Budgeted units = SAR, so budgeted cost = units x 1. Not counted in Units % complete.</t>
+          <t>Quantity carrier. Price 0, so it adds no budget cost. Set the price to 1 (and PROG-WT to 0) to see the contract-condition cost curve instead.</t>
         </is>
       </c>
     </row>
@@ -60458,7 +60458,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Progress weight (fair EPC distribution)</t>
+          <t>Progress weight (fair EPC distribution, SAR value)</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -60468,20 +60468,20 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Progress points: 100,000 points = 100% of the project. Fair EPC distribution (see Distribution_Keys)</t>
+          <t>Progress share x SAR 62,000,000 (100,000 points x SAR 620). Fair EPC distribution (see Distribution_Keys)</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Nonlabor resource with zero price. Activity % complete type is Units, so P6 measures progress with these points and the S-curve follows the points</t>
+          <t>Price 1, so budgeted cost = progress value in SAR. Activity % complete type is Physical, so earned value = physical % x this budget, and the cost and schedule performance indexes are measured in SAR on the progress distribution.</t>
         </is>
       </c>
     </row>

--- a/p6/SAR_BOQ_Cost_Mapping.xlsx
+++ b/p6/SAR_BOQ_Cost_Mapping.xlsx
@@ -60463,7 +60463,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Nonlabor</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">

--- a/p6/SAR_BOQ_Cost_Mapping.xlsx
+++ b/p6/SAR_BOQ_Cost_Mapping.xlsx
@@ -17,9 +17,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activity_Codes" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoicing_Monthly" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BOQ_Mapping'!$A$4:$T$474</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Invoicing_Monthly'!$A$4:$K$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,15 +29,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="170" formatCode="mmm-yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +72,12 @@
       <b val="1"/>
       <color rgb="0000778B"/>
       <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0000778B"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +151,9 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="17" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -340,6 +352,96 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cumulative invoiced %</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Invoicing_Monthly'!K94</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Invoicing_Monthly'!$A$95:$A$130</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Invoicing_Monthly'!$K$95:$K$130</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -347,6 +449,33 @@
       <col>7</col>
       <colOff>0</colOff>
       <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -760,7 +889,7 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>B9-B3</f>
+        <f>B10-B4</f>
         <v/>
       </c>
     </row>
@@ -795,7 +924,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Station_BOQ gives the BOQ value of each station; Payment_Milestones applies the contract payment conditions; BOQ_Mapping shows each activity cost; Distribution_Keys explains the keys; S_Curve shows cost against progress.</t>
+          <t>Station_BOQ gives the BOQ value of each station; Payment_Milestones applies the contract payment conditions; BOQ_Mapping shows each activity cost; Distribution_Keys explains the keys; S_Curve shows cost against progress; Invoicing_Monthly lists every invoice by month, milestone and station.</t>
         </is>
       </c>
     </row>
@@ -17943,6 +18072,8776 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q172"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Invoices per month, detailed: each payment milestone is invoiced in the month its milestone activity is achieved in the programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Amount = clause 15 payment milestone x Annex 3 station price (formulas link to Payment_Milestones). Invoice month = month of the trigger milestone date. Payment terms after invoicing (days to pay) are not modelled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Invoice month</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Milestone date</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Trigger activity ID</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Trigger activity</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Invoice amount (SAR)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Cumulative (SAR)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Cumulative %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>46369</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>MS1</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Mobilization</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>All stations</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>PRJ-M1100</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>MS1 Mobilization complete (payment milestone 20%)</t>
+        </is>
+      </c>
+      <c r="I5" s="9">
+        <f>Payment_Milestones!D5</f>
+        <v/>
+      </c>
+      <c r="J5" s="9">
+        <f>SUM(I$5:I5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>J5/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>46425</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Thumamah) (NRY)</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>NRY-E1200</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Riyadh (Thumamah)</t>
+        </is>
+      </c>
+      <c r="I6" s="9">
+        <f>Payment_Milestones!C16</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f>SUM(I$5:I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="23">
+        <f>J6/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>46439</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Malaz) (ERY)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>ERY-E1200</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Riyadh (Malaz)</t>
+        </is>
+      </c>
+      <c r="I7" s="9">
+        <f>Payment_Milestones!C17</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>SUM(I$5:I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="23">
+        <f>J7/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>46447</v>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Thumamah) (NRY)</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>NRY-E1210</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Riyadh (Thumamah)</t>
+        </is>
+      </c>
+      <c r="I8" s="9">
+        <f>Payment_Milestones!D16</f>
+        <v/>
+      </c>
+      <c r="J8" s="9">
+        <f>SUM(I$5:I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="23">
+        <f>J8/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>46468</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Malaz) (ERY)</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>ERY-E1210</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Riyadh (Malaz)</t>
+        </is>
+      </c>
+      <c r="I9" s="9">
+        <f>Payment_Milestones!D17</f>
+        <v/>
+      </c>
+      <c r="J9" s="9">
+        <f>SUM(I$5:I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="23">
+        <f>J9/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>46539</v>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>46562</v>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Jeddah (HJD)</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>HJD-E1200</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Jeddah</t>
+        </is>
+      </c>
+      <c r="I10" s="9">
+        <f>Payment_Milestones!C18</f>
+        <v/>
+      </c>
+      <c r="J10" s="9">
+        <f>SUM(I$5:I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="23">
+        <f>J10/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>46569</v>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>46583</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Jeddah (HJD)</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>HJD-E1210</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Jeddah</t>
+        </is>
+      </c>
+      <c r="I11" s="9">
+        <f>Payment_Milestones!D18</f>
+        <v/>
+      </c>
+      <c r="J11" s="9">
+        <f>SUM(I$5:I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="23">
+        <f>J11/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>46600</v>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>46601</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Thumamah) (NRY)</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>NRY-P1100</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Riyadh (Thumamah)</t>
+        </is>
+      </c>
+      <c r="I12" s="9">
+        <f>Payment_Milestones!E16</f>
+        <v/>
+      </c>
+      <c r="J12" s="9">
+        <f>SUM(I$5:I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="23">
+        <f>J12/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>46600</v>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>46615</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Malaz) (ERY)</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>ERY-P1100</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Riyadh (Malaz)</t>
+        </is>
+      </c>
+      <c r="I13" s="9">
+        <f>Payment_Milestones!E17</f>
+        <v/>
+      </c>
+      <c r="J13" s="9">
+        <f>SUM(I$5:I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="23">
+        <f>J13/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>46600</v>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>46618</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Dammam (EDM)</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>EDM-E1200</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Dammam</t>
+        </is>
+      </c>
+      <c r="I14" s="9">
+        <f>Payment_Milestones!C19</f>
+        <v/>
+      </c>
+      <c r="J14" s="9">
+        <f>SUM(I$5:I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="23">
+        <f>J14/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>46631</v>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>46639</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Dammam (EDM)</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>EDM-E1210</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Dammam</t>
+        </is>
+      </c>
+      <c r="I15" s="9">
+        <f>Payment_Milestones!D19</f>
+        <v/>
+      </c>
+      <c r="J15" s="9">
+        <f>SUM(I$5:I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="23">
+        <f>J15/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>46631</v>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>46651</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Thumamah) (NRY)</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>NRY-C2100</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Riyadh (Thumamah)</t>
+        </is>
+      </c>
+      <c r="I16" s="9">
+        <f>Payment_Milestones!F16</f>
+        <v/>
+      </c>
+      <c r="J16" s="9">
+        <f>SUM(I$5:I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="23">
+        <f>J16/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>46631</v>
+      </c>
+      <c r="B17" s="25" t="n">
+        <v>46658</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Malaz) (ERY)</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>ERY-C2100</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Riyadh (Malaz)</t>
+        </is>
+      </c>
+      <c r="I17" s="9">
+        <f>Payment_Milestones!F17</f>
+        <v/>
+      </c>
+      <c r="J17" s="9">
+        <f>SUM(I$5:I17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="23">
+        <f>J17/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B18" s="25" t="n">
+        <v>46673</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Thumamah) (NRY)</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>NRY-T1100</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Riyadh (Thumamah)</t>
+        </is>
+      </c>
+      <c r="I18" s="9">
+        <f>Payment_Milestones!G16</f>
+        <v/>
+      </c>
+      <c r="J18" s="9">
+        <f>SUM(I$5:I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="23">
+        <f>J18/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B19" s="25" t="n">
+        <v>46677</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Al Qassim (NQS)</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>NQS-E1200</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Al Qassim</t>
+        </is>
+      </c>
+      <c r="I19" s="9">
+        <f>Payment_Milestones!C20</f>
+        <v/>
+      </c>
+      <c r="J19" s="9">
+        <f>SUM(I$5:I19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="23">
+        <f>J19/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B20" s="25" t="n">
+        <v>46677</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Hufuf (EHF)</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>EHF-E1200</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Hufuf</t>
+        </is>
+      </c>
+      <c r="I20" s="9">
+        <f>Payment_Milestones!C21</f>
+        <v/>
+      </c>
+      <c r="J20" s="9">
+        <f>SUM(I$5:I20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="23">
+        <f>J20/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>46679</v>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Malaz) (ERY)</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>ERY-T1100</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Riyadh (Malaz)</t>
+        </is>
+      </c>
+      <c r="I21" s="9">
+        <f>Payment_Milestones!G17</f>
+        <v/>
+      </c>
+      <c r="J21" s="9">
+        <f>SUM(I$5:I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="23">
+        <f>J21/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n">
+        <v>46692</v>
+      </c>
+      <c r="B22" s="25" t="n">
+        <v>46698</v>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Al Qassim (NQS)</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>NQS-E1210</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Al Qassim</t>
+        </is>
+      </c>
+      <c r="I22" s="9">
+        <f>Payment_Milestones!D20</f>
+        <v/>
+      </c>
+      <c r="J22" s="9">
+        <f>SUM(I$5:I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="23">
+        <f>J22/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n">
+        <v>46692</v>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>46698</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Hufuf (EHF)</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>EHF-E1210</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Hufuf</t>
+        </is>
+      </c>
+      <c r="I23" s="9">
+        <f>Payment_Milestones!D21</f>
+        <v/>
+      </c>
+      <c r="J23" s="9">
+        <f>SUM(I$5:I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="23">
+        <f>J23/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>46726</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Al Majma'ah (NMJ)</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>NMJ-E1200</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Al Majma'ah</t>
+        </is>
+      </c>
+      <c r="I24" s="9">
+        <f>Payment_Milestones!C22</f>
+        <v/>
+      </c>
+      <c r="J24" s="9">
+        <f>SUM(I$5:I24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="23">
+        <f>J24/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>46729</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Thumamah) (NRY)</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>NRY-T3100</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Riyadh (Thumamah)</t>
+        </is>
+      </c>
+      <c r="I25" s="9">
+        <f>Payment_Milestones!H16</f>
+        <v/>
+      </c>
+      <c r="J25" s="9">
+        <f>SUM(I$5:I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="23">
+        <f>J25/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>46735</v>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Riyadh (Malaz) (ERY)</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>ERY-T3100</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Riyadh (Malaz)</t>
+        </is>
+      </c>
+      <c r="I26" s="9">
+        <f>Payment_Milestones!H17</f>
+        <v/>
+      </c>
+      <c r="J26" s="9">
+        <f>SUM(I$5:I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="23">
+        <f>J26/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>46747</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Al Majma'ah (NMJ)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>NMJ-E1210</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Al Majma'ah</t>
+        </is>
+      </c>
+      <c r="I27" s="9">
+        <f>Payment_Milestones!D22</f>
+        <v/>
+      </c>
+      <c r="J27" s="9">
+        <f>SUM(I$5:I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="23">
+        <f>J27/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="n">
+        <v>46753</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>46768</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Makkah (HMK)</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>HMK-E1200</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Makkah</t>
+        </is>
+      </c>
+      <c r="I28" s="9">
+        <f>Payment_Milestones!C23</f>
+        <v/>
+      </c>
+      <c r="J28" s="9">
+        <f>SUM(I$5:I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="23">
+        <f>J28/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="n">
+        <v>46753</v>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>46782</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Jeddah (HJD)</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>HJD-P1100</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Jeddah</t>
+        </is>
+      </c>
+      <c r="I29" s="9">
+        <f>Payment_Milestones!E18</f>
+        <v/>
+      </c>
+      <c r="J29" s="9">
+        <f>SUM(I$5:I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="23">
+        <f>J29/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n">
+        <v>46784</v>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>46789</v>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Makkah (HMK)</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>HMK-E1210</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Makkah</t>
+        </is>
+      </c>
+      <c r="I30" s="9">
+        <f>Payment_Milestones!D23</f>
+        <v/>
+      </c>
+      <c r="J30" s="9">
+        <f>SUM(I$5:I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="23">
+        <f>J30/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="n">
+        <v>46784</v>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>46796</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Dammam (EDM)</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>EDM-P1100</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Dammam</t>
+        </is>
+      </c>
+      <c r="I31" s="9">
+        <f>Payment_Milestones!E19</f>
+        <v/>
+      </c>
+      <c r="J31" s="9">
+        <f>SUM(I$5:I31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="23">
+        <f>J31/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="n">
+        <v>46844</v>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>46845</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Dammam (EDM)</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>EDM-C2100</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Dammam</t>
+        </is>
+      </c>
+      <c r="I32" s="9">
+        <f>Payment_Milestones!F19</f>
+        <v/>
+      </c>
+      <c r="J32" s="9">
+        <f>SUM(I$5:I32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="23">
+        <f>J32/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="n">
+        <v>46844</v>
+      </c>
+      <c r="B33" s="25" t="n">
+        <v>46859</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Al Qassim (NQS)</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>NQS-P1100</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Al Qassim</t>
+        </is>
+      </c>
+      <c r="I33" s="9">
+        <f>Payment_Milestones!E20</f>
+        <v/>
+      </c>
+      <c r="J33" s="9">
+        <f>SUM(I$5:I33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="23">
+        <f>J33/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="n">
+        <v>46844</v>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>46859</v>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Hufuf (EHF)</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>EHF-P1100</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Hufuf</t>
+        </is>
+      </c>
+      <c r="I34" s="9">
+        <f>Payment_Milestones!E21</f>
+        <v/>
+      </c>
+      <c r="J34" s="9">
+        <f>SUM(I$5:I34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="23">
+        <f>J34/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n">
+        <v>46844</v>
+      </c>
+      <c r="B35" s="25" t="n">
+        <v>46866</v>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Dammam (EDM)</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>EDM-T1100</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Dammam</t>
+        </is>
+      </c>
+      <c r="I35" s="9">
+        <f>Payment_Milestones!G19</f>
+        <v/>
+      </c>
+      <c r="J35" s="9">
+        <f>SUM(I$5:I35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="23">
+        <f>J35/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="n">
+        <v>46874</v>
+      </c>
+      <c r="B36" s="25" t="n">
+        <v>46904</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>KAEC (HKA)</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>HKA-E1200</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - KAEC</t>
+        </is>
+      </c>
+      <c r="I36" s="9">
+        <f>Payment_Milestones!C24</f>
+        <v/>
+      </c>
+      <c r="J36" s="9">
+        <f>SUM(I$5:I36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="23">
+        <f>J36/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="n">
+        <v>46874</v>
+      </c>
+      <c r="B37" s="25" t="n">
+        <v>46904</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Madinah (HMD)</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>HMD-E1200</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Madinah</t>
+        </is>
+      </c>
+      <c r="I37" s="9">
+        <f>Payment_Milestones!C25</f>
+        <v/>
+      </c>
+      <c r="J37" s="9">
+        <f>SUM(I$5:I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="23">
+        <f>J37/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B38" s="25" t="n">
+        <v>46908</v>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Hufuf (EHF)</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>EHF-C2100</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Hufuf</t>
+        </is>
+      </c>
+      <c r="I38" s="9">
+        <f>Payment_Milestones!F21</f>
+        <v/>
+      </c>
+      <c r="J38" s="9">
+        <f>SUM(I$5:I38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="23">
+        <f>J38/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B39" s="25" t="n">
+        <v>46911</v>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Abqaiq (EAB)</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>EAB-E1200</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Abqaiq</t>
+        </is>
+      </c>
+      <c r="I39" s="9">
+        <f>Payment_Milestones!C26</f>
+        <v/>
+      </c>
+      <c r="J39" s="9">
+        <f>SUM(I$5:I39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="23">
+        <f>J39/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B40" s="25" t="n">
+        <v>46915</v>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Al Majma'ah (NMJ)</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>NMJ-P1100</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Al Majma'ah</t>
+        </is>
+      </c>
+      <c r="I40" s="9">
+        <f>Payment_Milestones!E22</f>
+        <v/>
+      </c>
+      <c r="J40" s="9">
+        <f>SUM(I$5:I40)</f>
+        <v/>
+      </c>
+      <c r="K40" s="23">
+        <f>J40/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B41" s="25" t="n">
+        <v>46916</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Al Qassim (NQS)</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>NQS-C2100</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Al Qassim</t>
+        </is>
+      </c>
+      <c r="I41" s="9">
+        <f>Payment_Milestones!F20</f>
+        <v/>
+      </c>
+      <c r="J41" s="9">
+        <f>SUM(I$5:I41)</f>
+        <v/>
+      </c>
+      <c r="K41" s="23">
+        <f>J41/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B42" s="25" t="n">
+        <v>46922</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Jeddah (HJD)</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>HJD-C2100</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Jeddah</t>
+        </is>
+      </c>
+      <c r="I42" s="9">
+        <f>Payment_Milestones!F18</f>
+        <v/>
+      </c>
+      <c r="J42" s="9">
+        <f>SUM(I$5:I42)</f>
+        <v/>
+      </c>
+      <c r="K42" s="23">
+        <f>J42/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B43" s="25" t="n">
+        <v>46925</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>KAEC (HKA)</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>HKA-E1210</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - KAEC</t>
+        </is>
+      </c>
+      <c r="I43" s="9">
+        <f>Payment_Milestones!D24</f>
+        <v/>
+      </c>
+      <c r="J43" s="9">
+        <f>SUM(I$5:I43)</f>
+        <v/>
+      </c>
+      <c r="K43" s="23">
+        <f>J43/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B44" s="25" t="n">
+        <v>46925</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Madinah (HMD)</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>HMD-E1210</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Madinah</t>
+        </is>
+      </c>
+      <c r="I44" s="9">
+        <f>Payment_Milestones!D25</f>
+        <v/>
+      </c>
+      <c r="J44" s="9">
+        <f>SUM(I$5:I44)</f>
+        <v/>
+      </c>
+      <c r="K44" s="23">
+        <f>J44/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B45" s="25" t="n">
+        <v>46929</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Hufuf (EHF)</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>EHF-T1100</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Hufuf</t>
+        </is>
+      </c>
+      <c r="I45" s="9">
+        <f>Payment_Milestones!G21</f>
+        <v/>
+      </c>
+      <c r="J45" s="9">
+        <f>SUM(I$5:I45)</f>
+        <v/>
+      </c>
+      <c r="K45" s="23">
+        <f>J45/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B46" s="25" t="n">
+        <v>46929</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Dammam (EDM)</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>EDM-T3100</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Dammam</t>
+        </is>
+      </c>
+      <c r="I46" s="9">
+        <f>Payment_Milestones!H19</f>
+        <v/>
+      </c>
+      <c r="J46" s="9">
+        <f>SUM(I$5:I46)</f>
+        <v/>
+      </c>
+      <c r="K46" s="23">
+        <f>J46/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B47" s="25" t="n">
+        <v>46932</v>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Abqaiq (EAB)</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>EAB-E1210</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Abqaiq</t>
+        </is>
+      </c>
+      <c r="I47" s="9">
+        <f>Payment_Milestones!D26</f>
+        <v/>
+      </c>
+      <c r="J47" s="9">
+        <f>SUM(I$5:I47)</f>
+        <v/>
+      </c>
+      <c r="K47" s="23">
+        <f>J47/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B48" s="25" t="n">
+        <v>46937</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Hail (NHL)</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>NHL-E1200</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Hail</t>
+        </is>
+      </c>
+      <c r="I48" s="9">
+        <f>Payment_Milestones!C27</f>
+        <v/>
+      </c>
+      <c r="J48" s="9">
+        <f>SUM(I$5:I48)</f>
+        <v/>
+      </c>
+      <c r="K48" s="23">
+        <f>J48/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B49" s="25" t="n">
+        <v>46937</v>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Al Qassim (NQS)</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>NQS-T1100</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Al Qassim</t>
+        </is>
+      </c>
+      <c r="I49" s="9">
+        <f>Payment_Milestones!G20</f>
+        <v/>
+      </c>
+      <c r="J49" s="9">
+        <f>SUM(I$5:I49)</f>
+        <v/>
+      </c>
+      <c r="K49" s="23">
+        <f>J49/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B50" s="25" t="n">
+        <v>46957</v>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Jeddah (HJD)</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>HJD-T1100</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Jeddah</t>
+        </is>
+      </c>
+      <c r="I50" s="9">
+        <f>Payment_Milestones!G18</f>
+        <v/>
+      </c>
+      <c r="J50" s="9">
+        <f>SUM(I$5:I50)</f>
+        <v/>
+      </c>
+      <c r="K50" s="23">
+        <f>J50/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B51" s="25" t="n">
+        <v>46958</v>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Hail (NHL)</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>NHL-E1210</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Hail</t>
+        </is>
+      </c>
+      <c r="I51" s="9">
+        <f>Payment_Milestones!D27</f>
+        <v/>
+      </c>
+      <c r="J51" s="9">
+        <f>SUM(I$5:I51)</f>
+        <v/>
+      </c>
+      <c r="K51" s="23">
+        <f>J51/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B52" s="25" t="n">
+        <v>46965</v>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Al Majma'ah (NMJ)</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>NMJ-C2100</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Al Majma'ah</t>
+        </is>
+      </c>
+      <c r="I52" s="9">
+        <f>Payment_Milestones!F22</f>
+        <v/>
+      </c>
+      <c r="J52" s="9">
+        <f>SUM(I$5:I52)</f>
+        <v/>
+      </c>
+      <c r="K52" s="23">
+        <f>J52/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="n">
+        <v>46966</v>
+      </c>
+      <c r="B53" s="25" t="n">
+        <v>46985</v>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Hufuf (EHF)</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>EHF-T3100</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Hufuf</t>
+        </is>
+      </c>
+      <c r="I53" s="9">
+        <f>Payment_Milestones!H21</f>
+        <v/>
+      </c>
+      <c r="J53" s="9">
+        <f>SUM(I$5:I53)</f>
+        <v/>
+      </c>
+      <c r="K53" s="23">
+        <f>J53/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="n">
+        <v>46966</v>
+      </c>
+      <c r="B54" s="25" t="n">
+        <v>46986</v>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>Al Majma'ah (NMJ)</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>NMJ-T1100</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Al Majma'ah</t>
+        </is>
+      </c>
+      <c r="I54" s="9">
+        <f>Payment_Milestones!G22</f>
+        <v/>
+      </c>
+      <c r="J54" s="9">
+        <f>SUM(I$5:I54)</f>
+        <v/>
+      </c>
+      <c r="K54" s="23">
+        <f>J54/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="n">
+        <v>46966</v>
+      </c>
+      <c r="B55" s="25" t="n">
+        <v>46993</v>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Al Qassim (NQS)</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>NQS-T3100</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Al Qassim</t>
+        </is>
+      </c>
+      <c r="I55" s="9">
+        <f>Payment_Milestones!H20</f>
+        <v/>
+      </c>
+      <c r="J55" s="9">
+        <f>SUM(I$5:I55)</f>
+        <v/>
+      </c>
+      <c r="K55" s="23">
+        <f>J55/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="n">
+        <v>46997</v>
+      </c>
+      <c r="B56" s="25" t="n">
+        <v>46999</v>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Makkah (HMK)</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>HMK-P1100</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Makkah</t>
+        </is>
+      </c>
+      <c r="I56" s="9">
+        <f>Payment_Milestones!E23</f>
+        <v/>
+      </c>
+      <c r="J56" s="9">
+        <f>SUM(I$5:I56)</f>
+        <v/>
+      </c>
+      <c r="K56" s="23">
+        <f>J56/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="n">
+        <v>46997</v>
+      </c>
+      <c r="B57" s="25" t="n">
+        <v>47010</v>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Al Jouf (NJF)</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>NJF-E1200</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Al Jouf</t>
+        </is>
+      </c>
+      <c r="I57" s="9">
+        <f>Payment_Milestones!C28</f>
+        <v/>
+      </c>
+      <c r="J57" s="9">
+        <f>SUM(I$5:I57)</f>
+        <v/>
+      </c>
+      <c r="K57" s="23">
+        <f>J57/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="n">
+        <v>46997</v>
+      </c>
+      <c r="B58" s="25" t="n">
+        <v>47020</v>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Jeddah (HJD)</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>HJD-T3100</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Jeddah</t>
+        </is>
+      </c>
+      <c r="I58" s="9">
+        <f>Payment_Milestones!H18</f>
+        <v/>
+      </c>
+      <c r="J58" s="9">
+        <f>SUM(I$5:I58)</f>
+        <v/>
+      </c>
+      <c r="K58" s="23">
+        <f>J58/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="n">
+        <v>47027</v>
+      </c>
+      <c r="B59" s="25" t="n">
+        <v>47031</v>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Al Jouf (NJF)</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>NJF-E1210</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Al Jouf</t>
+        </is>
+      </c>
+      <c r="I59" s="9">
+        <f>Payment_Milestones!D28</f>
+        <v/>
+      </c>
+      <c r="J59" s="9">
+        <f>SUM(I$5:I59)</f>
+        <v/>
+      </c>
+      <c r="K59" s="23">
+        <f>J59/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="n">
+        <v>47027</v>
+      </c>
+      <c r="B60" s="25" t="n">
+        <v>47042</v>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Al Majma'ah (NMJ)</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>NMJ-T3100</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Al Majma'ah</t>
+        </is>
+      </c>
+      <c r="I60" s="9">
+        <f>Payment_Milestones!H22</f>
+        <v/>
+      </c>
+      <c r="J60" s="9">
+        <f>SUM(I$5:I60)</f>
+        <v/>
+      </c>
+      <c r="K60" s="23">
+        <f>J60/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="n">
+        <v>47058</v>
+      </c>
+      <c r="B61" s="25" t="n">
+        <v>47059</v>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Engineering submittal</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Al Qurayyat (NQR)</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>NQR-E1200</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>MS2 Engineering submittal complete (10%) - Al Qurayyat</t>
+        </is>
+      </c>
+      <c r="I61" s="9">
+        <f>Payment_Milestones!C29</f>
+        <v/>
+      </c>
+      <c r="J61" s="9">
+        <f>SUM(I$5:I61)</f>
+        <v/>
+      </c>
+      <c r="K61" s="23">
+        <f>J61/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="n">
+        <v>47058</v>
+      </c>
+      <c r="B62" s="25" t="n">
+        <v>47080</v>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>SAR approval of engineering</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Al Qurayyat (NQR)</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>NQR-E1210</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>MS3 Engineering approved by SAR (10%) - Al Qurayyat</t>
+        </is>
+      </c>
+      <c r="I62" s="9">
+        <f>Payment_Milestones!D29</f>
+        <v/>
+      </c>
+      <c r="J62" s="9">
+        <f>SUM(I$5:I62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="23">
+        <f>J62/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="n">
+        <v>47058</v>
+      </c>
+      <c r="B63" s="25" t="n">
+        <v>47086</v>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Abqaiq (EAB)</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>EAB-P1100</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Abqaiq</t>
+        </is>
+      </c>
+      <c r="I63" s="9">
+        <f>Payment_Milestones!E26</f>
+        <v/>
+      </c>
+      <c r="J63" s="9">
+        <f>SUM(I$5:I63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="23">
+        <f>J63/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="24" t="n">
+        <v>47088</v>
+      </c>
+      <c r="B64" s="25" t="n">
+        <v>47112</v>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Hail (NHL)</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>NHL-P1100</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Hail</t>
+        </is>
+      </c>
+      <c r="I64" s="9">
+        <f>Payment_Milestones!E27</f>
+        <v/>
+      </c>
+      <c r="J64" s="9">
+        <f>SUM(I$5:I64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="23">
+        <f>J64/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="n">
+        <v>47119</v>
+      </c>
+      <c r="B65" s="25" t="n">
+        <v>47121</v>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>KAEC (HKA)</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>HKA-P1100</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - KAEC</t>
+        </is>
+      </c>
+      <c r="I65" s="9">
+        <f>Payment_Milestones!E24</f>
+        <v/>
+      </c>
+      <c r="J65" s="9">
+        <f>SUM(I$5:I65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="23">
+        <f>J65/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="n">
+        <v>47119</v>
+      </c>
+      <c r="B66" s="25" t="n">
+        <v>47121</v>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Madinah (HMD)</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>HMD-P1100</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Madinah</t>
+        </is>
+      </c>
+      <c r="I66" s="9">
+        <f>Payment_Milestones!E25</f>
+        <v/>
+      </c>
+      <c r="J66" s="9">
+        <f>SUM(I$5:I66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="23">
+        <f>J66/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="24" t="n">
+        <v>47119</v>
+      </c>
+      <c r="B67" s="25" t="n">
+        <v>47122</v>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Abqaiq (EAB)</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>EAB-C2100</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Abqaiq</t>
+        </is>
+      </c>
+      <c r="I67" s="9">
+        <f>Payment_Milestones!F26</f>
+        <v/>
+      </c>
+      <c r="J67" s="9">
+        <f>SUM(I$5:I67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="23">
+        <f>J67/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="n">
+        <v>47119</v>
+      </c>
+      <c r="B68" s="25" t="n">
+        <v>47143</v>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Abqaiq (EAB)</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>EAB-T1100</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Abqaiq</t>
+        </is>
+      </c>
+      <c r="I68" s="9">
+        <f>Payment_Milestones!G26</f>
+        <v/>
+      </c>
+      <c r="J68" s="9">
+        <f>SUM(I$5:I68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="23">
+        <f>J68/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="n">
+        <v>47119</v>
+      </c>
+      <c r="B69" s="25" t="n">
+        <v>47147</v>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Makkah (HMK)</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>HMK-C2100</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Makkah</t>
+        </is>
+      </c>
+      <c r="I69" s="9">
+        <f>Payment_Milestones!F23</f>
+        <v/>
+      </c>
+      <c r="J69" s="9">
+        <f>SUM(I$5:I69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="23">
+        <f>J69/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="24" t="n">
+        <v>47150</v>
+      </c>
+      <c r="B70" s="25" t="n">
+        <v>47169</v>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Hail (NHL)</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>NHL-C2100</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Hail</t>
+        </is>
+      </c>
+      <c r="I70" s="9">
+        <f>Payment_Milestones!F27</f>
+        <v/>
+      </c>
+      <c r="J70" s="9">
+        <f>SUM(I$5:I70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="23">
+        <f>J70/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="n">
+        <v>47178</v>
+      </c>
+      <c r="B71" s="25" t="n">
+        <v>47190</v>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Makkah (HMK)</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>HMK-T1100</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Makkah</t>
+        </is>
+      </c>
+      <c r="I71" s="9">
+        <f>Payment_Milestones!G23</f>
+        <v/>
+      </c>
+      <c r="J71" s="9">
+        <f>SUM(I$5:I71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="23">
+        <f>J71/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="n">
+        <v>47178</v>
+      </c>
+      <c r="B72" s="25" t="n">
+        <v>47191</v>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Hail (NHL)</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>NHL-T1100</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Hail</t>
+        </is>
+      </c>
+      <c r="I72" s="9">
+        <f>Payment_Milestones!G27</f>
+        <v/>
+      </c>
+      <c r="J72" s="9">
+        <f>SUM(I$5:I72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="23">
+        <f>J72/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="24" t="n">
+        <v>47178</v>
+      </c>
+      <c r="B73" s="25" t="n">
+        <v>47195</v>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Al Jouf (NJF)</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>NJF-P1100</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Al Jouf</t>
+        </is>
+      </c>
+      <c r="I73" s="9">
+        <f>Payment_Milestones!E28</f>
+        <v/>
+      </c>
+      <c r="J73" s="9">
+        <f>SUM(I$5:I73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="23">
+        <f>J73/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="n">
+        <v>47209</v>
+      </c>
+      <c r="B74" s="25" t="n">
+        <v>47209</v>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Abqaiq (EAB)</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>EAB-T3100</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Abqaiq</t>
+        </is>
+      </c>
+      <c r="I74" s="9">
+        <f>Payment_Milestones!H26</f>
+        <v/>
+      </c>
+      <c r="J74" s="9">
+        <f>SUM(I$5:I74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="23">
+        <f>J74/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="n">
+        <v>47209</v>
+      </c>
+      <c r="B75" s="25" t="n">
+        <v>47223</v>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>KAEC (HKA)</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>HKA-C2100</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - KAEC</t>
+        </is>
+      </c>
+      <c r="I75" s="9">
+        <f>Payment_Milestones!F24</f>
+        <v/>
+      </c>
+      <c r="J75" s="9">
+        <f>SUM(I$5:I75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="23">
+        <f>J75/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="n">
+        <v>47209</v>
+      </c>
+      <c r="B76" s="25" t="n">
+        <v>47227</v>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Madinah (HMD)</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>HMD-C2100</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Madinah</t>
+        </is>
+      </c>
+      <c r="I76" s="9">
+        <f>Payment_Milestones!F25</f>
+        <v/>
+      </c>
+      <c r="J76" s="9">
+        <f>SUM(I$5:I76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="23">
+        <f>J76/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="24" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B77" s="25" t="n">
+        <v>47251</v>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Material delivery</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Al Qurayyat (NQR)</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>NQR-P1100</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>MS4 Material delivered (20%) - Al Qurayyat</t>
+        </is>
+      </c>
+      <c r="I77" s="9">
+        <f>Payment_Milestones!E29</f>
+        <v/>
+      </c>
+      <c r="J77" s="9">
+        <f>SUM(I$5:I77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="23">
+        <f>J77/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B78" s="25" t="n">
+        <v>47252</v>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Al Jouf (NJF)</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>NJF-C2100</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Al Jouf</t>
+        </is>
+      </c>
+      <c r="I78" s="9">
+        <f>Payment_Milestones!F28</f>
+        <v/>
+      </c>
+      <c r="J78" s="9">
+        <f>SUM(I$5:I78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="23">
+        <f>J78/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="24" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B79" s="25" t="n">
+        <v>47254</v>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>Hail (NHL)</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>NHL-T3100</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Hail</t>
+        </is>
+      </c>
+      <c r="I79" s="9">
+        <f>Payment_Milestones!H27</f>
+        <v/>
+      </c>
+      <c r="J79" s="9">
+        <f>SUM(I$5:I79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="23">
+        <f>J79/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="24" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B80" s="25" t="n">
+        <v>47260</v>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>Makkah (HMK)</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>HMK-T3100</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Makkah</t>
+        </is>
+      </c>
+      <c r="I80" s="9">
+        <f>Payment_Milestones!H23</f>
+        <v/>
+      </c>
+      <c r="J80" s="9">
+        <f>SUM(I$5:I80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="23">
+        <f>J80/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B81" s="25" t="n">
+        <v>47265</v>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>KAEC (HKA)</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>HKA-T1100</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - KAEC</t>
+        </is>
+      </c>
+      <c r="I81" s="9">
+        <f>Payment_Milestones!G24</f>
+        <v/>
+      </c>
+      <c r="J81" s="9">
+        <f>SUM(I$5:I81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="23">
+        <f>J81/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B82" s="25" t="n">
+        <v>47269</v>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Madinah (HMD)</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>HMD-T1100</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Madinah</t>
+        </is>
+      </c>
+      <c r="I82" s="9">
+        <f>Payment_Milestones!G25</f>
+        <v/>
+      </c>
+      <c r="J82" s="9">
+        <f>SUM(I$5:I82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="23">
+        <f>J82/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="24" t="n">
+        <v>47270</v>
+      </c>
+      <c r="B83" s="25" t="n">
+        <v>47273</v>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>Al Jouf (NJF)</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>NJF-T1100</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Al Jouf</t>
+        </is>
+      </c>
+      <c r="I83" s="9">
+        <f>Payment_Milestones!G28</f>
+        <v/>
+      </c>
+      <c r="J83" s="9">
+        <f>SUM(I$5:I83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="23">
+        <f>J83/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="n">
+        <v>47300</v>
+      </c>
+      <c r="B84" s="25" t="n">
+        <v>47301</v>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Al Qurayyat (NQR)</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>NQR-C2100</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>MS5 Installation complete (20%) - Al Qurayyat</t>
+        </is>
+      </c>
+      <c r="I84" s="9">
+        <f>Payment_Milestones!F29</f>
+        <v/>
+      </c>
+      <c r="J84" s="9">
+        <f>SUM(I$5:I84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="23">
+        <f>J84/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="n">
+        <v>47300</v>
+      </c>
+      <c r="B85" s="25" t="n">
+        <v>47322</v>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Testing and commissioning (SAT)</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>Al Qurayyat (NQR)</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>NQR-T1100</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>MS6 SAT complete (10%) - Al Qurayyat</t>
+        </is>
+      </c>
+      <c r="I85" s="9">
+        <f>Payment_Milestones!G29</f>
+        <v/>
+      </c>
+      <c r="J85" s="9">
+        <f>SUM(I$5:I85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="23">
+        <f>J85/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="24" t="n">
+        <v>47300</v>
+      </c>
+      <c r="B86" s="25" t="n">
+        <v>47328</v>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>KAEC (HKA)</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>HKA-T3100</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - KAEC</t>
+        </is>
+      </c>
+      <c r="I86" s="9">
+        <f>Payment_Milestones!H24</f>
+        <v/>
+      </c>
+      <c r="J86" s="9">
+        <f>SUM(I$5:I86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="23">
+        <f>J86/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="n">
+        <v>47300</v>
+      </c>
+      <c r="B87" s="25" t="n">
+        <v>47329</v>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Al Jouf (NJF)</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>NJF-T3100</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Al Jouf</t>
+        </is>
+      </c>
+      <c r="I87" s="9">
+        <f>Payment_Milestones!H28</f>
+        <v/>
+      </c>
+      <c r="J87" s="9">
+        <f>SUM(I$5:I87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="23">
+        <f>J87/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="24" t="n">
+        <v>47331</v>
+      </c>
+      <c r="B88" s="25" t="n">
+        <v>47332</v>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>Madinah (HMD)</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>HHR</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>HMD-T3100</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Madinah</t>
+        </is>
+      </c>
+      <c r="I88" s="9">
+        <f>Payment_Milestones!H25</f>
+        <v/>
+      </c>
+      <c r="J88" s="9">
+        <f>SUM(I$5:I88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="23">
+        <f>J88/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="n">
+        <v>47362</v>
+      </c>
+      <c r="B89" s="25" t="n">
+        <v>47378</v>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Final acceptance and handover</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>Al Qurayyat (NQR)</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>NSR</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>NQR-T3100</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>MS7 Station accepted - final acceptance and handover (10%) - Al Qurayyat</t>
+        </is>
+      </c>
+      <c r="I89" s="9">
+        <f>Payment_Milestones!H29</f>
+        <v/>
+      </c>
+      <c r="J89" s="9">
+        <f>SUM(I$5:I89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="23">
+        <f>J89/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr"/>
+      <c r="C90" s="11" t="inlineStr"/>
+      <c r="D90" s="11" t="inlineStr"/>
+      <c r="E90" s="11" t="inlineStr"/>
+      <c r="F90" s="11" t="inlineStr"/>
+      <c r="G90" s="11" t="inlineStr"/>
+      <c r="H90" s="11" t="inlineStr"/>
+      <c r="I90" s="12">
+        <f>SUM(I5:I89)</f>
+        <v/>
+      </c>
+      <c r="J90" s="11" t="inlineStr"/>
+      <c r="K90" s="11" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Difference to contract price (should be 0)</t>
+        </is>
+      </c>
+      <c r="I91" s="15">
+        <f>I90-62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>Monthly invoicing by payment milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>MS1</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>MS6</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>MS7</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>Invoiced in month (SAR)</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>Cumulative invoiced (SAR)</t>
+        </is>
+      </c>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>Cumulative %</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B95" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A95,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C95" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A95,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D95" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A95,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E95" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A95,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F95" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A95,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G95" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A95,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H95" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A95,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I95" s="9">
+        <f>SUM(B95:H95)</f>
+        <v/>
+      </c>
+      <c r="J95" s="9">
+        <f>SUM(I$95:I95)</f>
+        <v/>
+      </c>
+      <c r="K95" s="23">
+        <f>J95/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B96" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A96,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C96" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A96,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D96" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A96,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E96" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A96,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F96" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A96,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G96" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A96,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H96" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A96,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I96" s="9">
+        <f>SUM(B96:H96)</f>
+        <v/>
+      </c>
+      <c r="J96" s="9">
+        <f>SUM(I$95:I96)</f>
+        <v/>
+      </c>
+      <c r="K96" s="23">
+        <f>J96/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B97" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A97,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C97" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A97,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D97" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A97,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E97" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A97,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F97" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A97,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G97" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A97,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H97" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A97,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I97" s="9">
+        <f>SUM(B97:H97)</f>
+        <v/>
+      </c>
+      <c r="J97" s="9">
+        <f>SUM(I$95:I97)</f>
+        <v/>
+      </c>
+      <c r="K97" s="23">
+        <f>J97/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B98" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A98,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C98" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A98,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D98" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A98,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E98" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A98,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F98" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A98,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G98" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A98,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H98" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A98,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I98" s="9">
+        <f>SUM(B98:H98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="9">
+        <f>SUM(I$95:I98)</f>
+        <v/>
+      </c>
+      <c r="K98" s="23">
+        <f>J98/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B99" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A99,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C99" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A99,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D99" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A99,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E99" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A99,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F99" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A99,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G99" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A99,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H99" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A99,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I99" s="9">
+        <f>SUM(B99:H99)</f>
+        <v/>
+      </c>
+      <c r="J99" s="9">
+        <f>SUM(I$95:I99)</f>
+        <v/>
+      </c>
+      <c r="K99" s="23">
+        <f>J99/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B100" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A100,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C100" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A100,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D100" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A100,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E100" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A100,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F100" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A100,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G100" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A100,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H100" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A100,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I100" s="9">
+        <f>SUM(B100:H100)</f>
+        <v/>
+      </c>
+      <c r="J100" s="9">
+        <f>SUM(I$95:I100)</f>
+        <v/>
+      </c>
+      <c r="K100" s="23">
+        <f>J100/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="24" t="n">
+        <v>46508</v>
+      </c>
+      <c r="B101" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A101,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C101" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A101,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D101" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A101,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E101" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A101,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F101" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A101,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G101" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A101,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H101" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A101,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I101" s="9">
+        <f>SUM(B101:H101)</f>
+        <v/>
+      </c>
+      <c r="J101" s="9">
+        <f>SUM(I$95:I101)</f>
+        <v/>
+      </c>
+      <c r="K101" s="23">
+        <f>J101/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="24" t="n">
+        <v>46539</v>
+      </c>
+      <c r="B102" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A102,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C102" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A102,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D102" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A102,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E102" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A102,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F102" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A102,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G102" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A102,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H102" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A102,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I102" s="9">
+        <f>SUM(B102:H102)</f>
+        <v/>
+      </c>
+      <c r="J102" s="9">
+        <f>SUM(I$95:I102)</f>
+        <v/>
+      </c>
+      <c r="K102" s="23">
+        <f>J102/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="24" t="n">
+        <v>46569</v>
+      </c>
+      <c r="B103" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A103,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C103" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A103,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D103" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A103,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E103" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A103,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F103" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A103,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G103" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A103,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H103" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A103,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I103" s="9">
+        <f>SUM(B103:H103)</f>
+        <v/>
+      </c>
+      <c r="J103" s="9">
+        <f>SUM(I$95:I103)</f>
+        <v/>
+      </c>
+      <c r="K103" s="23">
+        <f>J103/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="24" t="n">
+        <v>46600</v>
+      </c>
+      <c r="B104" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A104,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C104" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A104,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D104" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A104,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E104" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A104,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F104" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A104,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G104" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A104,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H104" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A104,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I104" s="9">
+        <f>SUM(B104:H104)</f>
+        <v/>
+      </c>
+      <c r="J104" s="9">
+        <f>SUM(I$95:I104)</f>
+        <v/>
+      </c>
+      <c r="K104" s="23">
+        <f>J104/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="24" t="n">
+        <v>46631</v>
+      </c>
+      <c r="B105" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A105,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C105" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A105,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D105" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A105,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E105" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A105,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F105" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A105,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G105" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A105,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H105" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A105,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I105" s="9">
+        <f>SUM(B105:H105)</f>
+        <v/>
+      </c>
+      <c r="J105" s="9">
+        <f>SUM(I$95:I105)</f>
+        <v/>
+      </c>
+      <c r="K105" s="23">
+        <f>J105/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="24" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B106" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A106,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C106" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A106,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D106" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A106,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E106" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A106,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F106" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A106,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G106" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A106,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H106" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A106,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I106" s="9">
+        <f>SUM(B106:H106)</f>
+        <v/>
+      </c>
+      <c r="J106" s="9">
+        <f>SUM(I$95:I106)</f>
+        <v/>
+      </c>
+      <c r="K106" s="23">
+        <f>J106/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="24" t="n">
+        <v>46692</v>
+      </c>
+      <c r="B107" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A107,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C107" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A107,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D107" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A107,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E107" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A107,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F107" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A107,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G107" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A107,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H107" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A107,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I107" s="9">
+        <f>SUM(B107:H107)</f>
+        <v/>
+      </c>
+      <c r="J107" s="9">
+        <f>SUM(I$95:I107)</f>
+        <v/>
+      </c>
+      <c r="K107" s="23">
+        <f>J107/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="24" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B108" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A108,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C108" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A108,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D108" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A108,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E108" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A108,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F108" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A108,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G108" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A108,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H108" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A108,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I108" s="9">
+        <f>SUM(B108:H108)</f>
+        <v/>
+      </c>
+      <c r="J108" s="9">
+        <f>SUM(I$95:I108)</f>
+        <v/>
+      </c>
+      <c r="K108" s="23">
+        <f>J108/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="24" t="n">
+        <v>46753</v>
+      </c>
+      <c r="B109" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A109,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C109" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A109,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D109" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A109,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E109" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A109,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F109" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A109,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G109" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A109,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H109" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A109,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I109" s="9">
+        <f>SUM(B109:H109)</f>
+        <v/>
+      </c>
+      <c r="J109" s="9">
+        <f>SUM(I$95:I109)</f>
+        <v/>
+      </c>
+      <c r="K109" s="23">
+        <f>J109/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="24" t="n">
+        <v>46784</v>
+      </c>
+      <c r="B110" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A110,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C110" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A110,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D110" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A110,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E110" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A110,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F110" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A110,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G110" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A110,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H110" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A110,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I110" s="9">
+        <f>SUM(B110:H110)</f>
+        <v/>
+      </c>
+      <c r="J110" s="9">
+        <f>SUM(I$95:I110)</f>
+        <v/>
+      </c>
+      <c r="K110" s="23">
+        <f>J110/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="24" t="n">
+        <v>46813</v>
+      </c>
+      <c r="B111" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A111,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C111" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A111,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D111" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A111,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E111" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A111,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F111" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A111,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G111" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A111,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H111" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A111,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I111" s="9">
+        <f>SUM(B111:H111)</f>
+        <v/>
+      </c>
+      <c r="J111" s="9">
+        <f>SUM(I$95:I111)</f>
+        <v/>
+      </c>
+      <c r="K111" s="23">
+        <f>J111/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="24" t="n">
+        <v>46844</v>
+      </c>
+      <c r="B112" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A112,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C112" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A112,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D112" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A112,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E112" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A112,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F112" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A112,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G112" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A112,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H112" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A112,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I112" s="9">
+        <f>SUM(B112:H112)</f>
+        <v/>
+      </c>
+      <c r="J112" s="9">
+        <f>SUM(I$95:I112)</f>
+        <v/>
+      </c>
+      <c r="K112" s="23">
+        <f>J112/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="24" t="n">
+        <v>46874</v>
+      </c>
+      <c r="B113" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A113,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C113" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A113,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D113" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A113,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E113" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A113,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F113" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A113,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G113" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A113,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H113" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A113,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I113" s="9">
+        <f>SUM(B113:H113)</f>
+        <v/>
+      </c>
+      <c r="J113" s="9">
+        <f>SUM(I$95:I113)</f>
+        <v/>
+      </c>
+      <c r="K113" s="23">
+        <f>J113/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B114" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A114,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C114" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A114,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D114" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A114,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E114" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A114,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F114" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A114,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G114" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A114,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H114" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A114,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I114" s="9">
+        <f>SUM(B114:H114)</f>
+        <v/>
+      </c>
+      <c r="J114" s="9">
+        <f>SUM(I$95:I114)</f>
+        <v/>
+      </c>
+      <c r="K114" s="23">
+        <f>J114/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="24" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B115" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A115,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C115" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A115,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D115" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A115,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E115" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A115,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F115" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A115,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G115" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A115,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H115" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A115,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I115" s="9">
+        <f>SUM(B115:H115)</f>
+        <v/>
+      </c>
+      <c r="J115" s="9">
+        <f>SUM(I$95:I115)</f>
+        <v/>
+      </c>
+      <c r="K115" s="23">
+        <f>J115/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="24" t="n">
+        <v>46966</v>
+      </c>
+      <c r="B116" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A116,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C116" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A116,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D116" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A116,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E116" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A116,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F116" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A116,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G116" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A116,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H116" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A116,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I116" s="9">
+        <f>SUM(B116:H116)</f>
+        <v/>
+      </c>
+      <c r="J116" s="9">
+        <f>SUM(I$95:I116)</f>
+        <v/>
+      </c>
+      <c r="K116" s="23">
+        <f>J116/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="24" t="n">
+        <v>46997</v>
+      </c>
+      <c r="B117" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A117,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C117" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A117,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D117" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A117,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E117" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A117,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F117" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A117,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G117" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A117,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H117" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A117,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I117" s="9">
+        <f>SUM(B117:H117)</f>
+        <v/>
+      </c>
+      <c r="J117" s="9">
+        <f>SUM(I$95:I117)</f>
+        <v/>
+      </c>
+      <c r="K117" s="23">
+        <f>J117/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="24" t="n">
+        <v>47027</v>
+      </c>
+      <c r="B118" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A118,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C118" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A118,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D118" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A118,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E118" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A118,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F118" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A118,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G118" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A118,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H118" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A118,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I118" s="9">
+        <f>SUM(B118:H118)</f>
+        <v/>
+      </c>
+      <c r="J118" s="9">
+        <f>SUM(I$95:I118)</f>
+        <v/>
+      </c>
+      <c r="K118" s="23">
+        <f>J118/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="24" t="n">
+        <v>47058</v>
+      </c>
+      <c r="B119" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A119,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C119" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A119,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D119" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A119,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E119" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A119,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F119" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A119,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G119" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A119,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H119" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A119,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I119" s="9">
+        <f>SUM(B119:H119)</f>
+        <v/>
+      </c>
+      <c r="J119" s="9">
+        <f>SUM(I$95:I119)</f>
+        <v/>
+      </c>
+      <c r="K119" s="23">
+        <f>J119/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="24" t="n">
+        <v>47088</v>
+      </c>
+      <c r="B120" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A120,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C120" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A120,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D120" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A120,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E120" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A120,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F120" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A120,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G120" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A120,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H120" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A120,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I120" s="9">
+        <f>SUM(B120:H120)</f>
+        <v/>
+      </c>
+      <c r="J120" s="9">
+        <f>SUM(I$95:I120)</f>
+        <v/>
+      </c>
+      <c r="K120" s="23">
+        <f>J120/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="24" t="n">
+        <v>47119</v>
+      </c>
+      <c r="B121" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A121,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C121" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A121,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D121" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A121,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E121" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A121,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F121" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A121,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G121" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A121,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H121" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A121,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I121" s="9">
+        <f>SUM(B121:H121)</f>
+        <v/>
+      </c>
+      <c r="J121" s="9">
+        <f>SUM(I$95:I121)</f>
+        <v/>
+      </c>
+      <c r="K121" s="23">
+        <f>J121/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="24" t="n">
+        <v>47150</v>
+      </c>
+      <c r="B122" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A122,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C122" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A122,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D122" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A122,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E122" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A122,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F122" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A122,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G122" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A122,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H122" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A122,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I122" s="9">
+        <f>SUM(B122:H122)</f>
+        <v/>
+      </c>
+      <c r="J122" s="9">
+        <f>SUM(I$95:I122)</f>
+        <v/>
+      </c>
+      <c r="K122" s="23">
+        <f>J122/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="24" t="n">
+        <v>47178</v>
+      </c>
+      <c r="B123" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A123,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C123" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A123,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D123" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A123,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E123" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A123,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F123" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A123,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G123" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A123,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H123" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A123,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I123" s="9">
+        <f>SUM(B123:H123)</f>
+        <v/>
+      </c>
+      <c r="J123" s="9">
+        <f>SUM(I$95:I123)</f>
+        <v/>
+      </c>
+      <c r="K123" s="23">
+        <f>J123/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="24" t="n">
+        <v>47209</v>
+      </c>
+      <c r="B124" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A124,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C124" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A124,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D124" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A124,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E124" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A124,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F124" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A124,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G124" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A124,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H124" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A124,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I124" s="9">
+        <f>SUM(B124:H124)</f>
+        <v/>
+      </c>
+      <c r="J124" s="9">
+        <f>SUM(I$95:I124)</f>
+        <v/>
+      </c>
+      <c r="K124" s="23">
+        <f>J124/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="24" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B125" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A125,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C125" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A125,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D125" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A125,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E125" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A125,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F125" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A125,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G125" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A125,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H125" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A125,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I125" s="9">
+        <f>SUM(B125:H125)</f>
+        <v/>
+      </c>
+      <c r="J125" s="9">
+        <f>SUM(I$95:I125)</f>
+        <v/>
+      </c>
+      <c r="K125" s="23">
+        <f>J125/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="24" t="n">
+        <v>47270</v>
+      </c>
+      <c r="B126" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A126,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C126" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A126,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D126" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A126,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E126" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A126,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F126" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A126,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G126" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A126,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H126" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A126,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I126" s="9">
+        <f>SUM(B126:H126)</f>
+        <v/>
+      </c>
+      <c r="J126" s="9">
+        <f>SUM(I$95:I126)</f>
+        <v/>
+      </c>
+      <c r="K126" s="23">
+        <f>J126/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="24" t="n">
+        <v>47300</v>
+      </c>
+      <c r="B127" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A127,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C127" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A127,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D127" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A127,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E127" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A127,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F127" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A127,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G127" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A127,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H127" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A127,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I127" s="9">
+        <f>SUM(B127:H127)</f>
+        <v/>
+      </c>
+      <c r="J127" s="9">
+        <f>SUM(I$95:I127)</f>
+        <v/>
+      </c>
+      <c r="K127" s="23">
+        <f>J127/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="24" t="n">
+        <v>47331</v>
+      </c>
+      <c r="B128" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A128,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C128" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A128,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D128" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A128,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E128" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A128,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F128" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A128,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G128" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A128,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H128" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A128,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I128" s="9">
+        <f>SUM(B128:H128)</f>
+        <v/>
+      </c>
+      <c r="J128" s="9">
+        <f>SUM(I$95:I128)</f>
+        <v/>
+      </c>
+      <c r="K128" s="23">
+        <f>J128/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="24" t="n">
+        <v>47362</v>
+      </c>
+      <c r="B129" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A129,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C129" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A129,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D129" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A129,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E129" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A129,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F129" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A129,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G129" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A129,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H129" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A129,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I129" s="9">
+        <f>SUM(B129:H129)</f>
+        <v/>
+      </c>
+      <c r="J129" s="9">
+        <f>SUM(I$95:I129)</f>
+        <v/>
+      </c>
+      <c r="K129" s="23">
+        <f>J129/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="24" t="n">
+        <v>47392</v>
+      </c>
+      <c r="B130" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A130,$C$5:$C$89,B$94)</f>
+        <v/>
+      </c>
+      <c r="C130" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A130,$C$5:$C$89,C$94)</f>
+        <v/>
+      </c>
+      <c r="D130" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A130,$C$5:$C$89,D$94)</f>
+        <v/>
+      </c>
+      <c r="E130" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A130,$C$5:$C$89,E$94)</f>
+        <v/>
+      </c>
+      <c r="F130" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A130,$C$5:$C$89,F$94)</f>
+        <v/>
+      </c>
+      <c r="G130" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A130,$C$5:$C$89,G$94)</f>
+        <v/>
+      </c>
+      <c r="H130" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A130,$C$5:$C$89,H$94)</f>
+        <v/>
+      </c>
+      <c r="I130" s="9">
+        <f>SUM(B130:H130)</f>
+        <v/>
+      </c>
+      <c r="J130" s="9">
+        <f>SUM(I$95:I130)</f>
+        <v/>
+      </c>
+      <c r="K130" s="23">
+        <f>J130/62000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B131" s="12">
+        <f>SUM(B95:B130)</f>
+        <v/>
+      </c>
+      <c r="C131" s="12">
+        <f>SUM(C95:C130)</f>
+        <v/>
+      </c>
+      <c r="D131" s="12">
+        <f>SUM(D95:D130)</f>
+        <v/>
+      </c>
+      <c r="E131" s="12">
+        <f>SUM(E95:E130)</f>
+        <v/>
+      </c>
+      <c r="F131" s="12">
+        <f>SUM(F95:F130)</f>
+        <v/>
+      </c>
+      <c r="G131" s="12">
+        <f>SUM(G95:G130)</f>
+        <v/>
+      </c>
+      <c r="H131" s="12">
+        <f>SUM(H95:H130)</f>
+        <v/>
+      </c>
+      <c r="I131" s="12">
+        <f>SUM(I95:I130)</f>
+        <v/>
+      </c>
+      <c r="J131" s="11" t="inlineStr"/>
+      <c r="K131" s="11" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="26" t="inlineStr">
+        <is>
+          <t>Monthly invoicing by station (MS2 to MS7 per station, MS1 shown as project level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="32" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>All stations</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Riyadh (Thumamah) (NRY)</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Riyadh (Malaz) (ERY)</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>Jeddah (HJD)</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Dammam (EDM)</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Al Qassim (NQS)</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>Hufuf (EHF)</t>
+        </is>
+      </c>
+      <c r="I135" s="7" t="inlineStr">
+        <is>
+          <t>Al Majma'ah (NMJ)</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>Makkah (HMK)</t>
+        </is>
+      </c>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t>KAEC (HKA)</t>
+        </is>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>Madinah (HMD)</t>
+        </is>
+      </c>
+      <c r="M135" s="7" t="inlineStr">
+        <is>
+          <t>Abqaiq (EAB)</t>
+        </is>
+      </c>
+      <c r="N135" s="7" t="inlineStr">
+        <is>
+          <t>Hail (NHL)</t>
+        </is>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t>Al Jouf (NJF)</t>
+        </is>
+      </c>
+      <c r="P135" s="7" t="inlineStr">
+        <is>
+          <t>Al Qurayyat (NQR)</t>
+        </is>
+      </c>
+      <c r="Q135" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="24" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P136" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A136,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q136" s="9">
+        <f>SUM(B136:P136)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="24" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P137" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A137,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q137" s="9">
+        <f>SUM(B137:P137)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="24" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P138" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A138,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q138" s="9">
+        <f>SUM(B138:P138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="24" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P139" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A139,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q139" s="9">
+        <f>SUM(B139:P139)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="24" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P140" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A140,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q140" s="9">
+        <f>SUM(B140:P140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="24" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P141" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A141,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q141" s="9">
+        <f>SUM(B141:P141)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="24" t="n">
+        <v>46508</v>
+      </c>
+      <c r="B142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P142" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A142,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q142" s="9">
+        <f>SUM(B142:P142)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="24" t="n">
+        <v>46539</v>
+      </c>
+      <c r="B143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P143" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A143,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q143" s="9">
+        <f>SUM(B143:P143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="24" t="n">
+        <v>46569</v>
+      </c>
+      <c r="B144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P144" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A144,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q144" s="9">
+        <f>SUM(B144:P144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="24" t="n">
+        <v>46600</v>
+      </c>
+      <c r="B145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P145" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A145,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q145" s="9">
+        <f>SUM(B145:P145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="24" t="n">
+        <v>46631</v>
+      </c>
+      <c r="B146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P146" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A146,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q146" s="9">
+        <f>SUM(B146:P146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="24" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P147" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A147,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q147" s="9">
+        <f>SUM(B147:P147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="24" t="n">
+        <v>46692</v>
+      </c>
+      <c r="B148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P148" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A148,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q148" s="9">
+        <f>SUM(B148:P148)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="24" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P149" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A149,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q149" s="9">
+        <f>SUM(B149:P149)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="24" t="n">
+        <v>46753</v>
+      </c>
+      <c r="B150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P150" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A150,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q150" s="9">
+        <f>SUM(B150:P150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="24" t="n">
+        <v>46784</v>
+      </c>
+      <c r="B151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P151" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A151,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q151" s="9">
+        <f>SUM(B151:P151)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="24" t="n">
+        <v>46813</v>
+      </c>
+      <c r="B152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P152" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A152,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q152" s="9">
+        <f>SUM(B152:P152)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="24" t="n">
+        <v>46844</v>
+      </c>
+      <c r="B153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P153" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A153,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q153" s="9">
+        <f>SUM(B153:P153)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="24" t="n">
+        <v>46874</v>
+      </c>
+      <c r="B154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P154" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A154,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q154" s="9">
+        <f>SUM(B154:P154)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="24" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P155" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A155,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q155" s="9">
+        <f>SUM(B155:P155)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="24" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P156" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A156,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q156" s="9">
+        <f>SUM(B156:P156)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="24" t="n">
+        <v>46966</v>
+      </c>
+      <c r="B157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P157" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A157,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q157" s="9">
+        <f>SUM(B157:P157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="24" t="n">
+        <v>46997</v>
+      </c>
+      <c r="B158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P158" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A158,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q158" s="9">
+        <f>SUM(B158:P158)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="24" t="n">
+        <v>47027</v>
+      </c>
+      <c r="B159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P159" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A159,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q159" s="9">
+        <f>SUM(B159:P159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="24" t="n">
+        <v>47058</v>
+      </c>
+      <c r="B160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P160" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A160,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q160" s="9">
+        <f>SUM(B160:P160)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="24" t="n">
+        <v>47088</v>
+      </c>
+      <c r="B161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P161" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A161,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q161" s="9">
+        <f>SUM(B161:P161)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="24" t="n">
+        <v>47119</v>
+      </c>
+      <c r="B162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P162" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A162,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q162" s="9">
+        <f>SUM(B162:P162)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="24" t="n">
+        <v>47150</v>
+      </c>
+      <c r="B163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P163" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A163,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q163" s="9">
+        <f>SUM(B163:P163)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="24" t="n">
+        <v>47178</v>
+      </c>
+      <c r="B164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P164" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A164,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q164" s="9">
+        <f>SUM(B164:P164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="24" t="n">
+        <v>47209</v>
+      </c>
+      <c r="B165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P165" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A165,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q165" s="9">
+        <f>SUM(B165:P165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="24" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P166" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A166,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q166" s="9">
+        <f>SUM(B166:P166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="24" t="n">
+        <v>47270</v>
+      </c>
+      <c r="B167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P167" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A167,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q167" s="9">
+        <f>SUM(B167:P167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="24" t="n">
+        <v>47300</v>
+      </c>
+      <c r="B168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P168" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A168,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q168" s="9">
+        <f>SUM(B168:P168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="24" t="n">
+        <v>47331</v>
+      </c>
+      <c r="B169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P169" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A169,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q169" s="9">
+        <f>SUM(B169:P169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="24" t="n">
+        <v>47362</v>
+      </c>
+      <c r="B170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P170" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A170,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q170" s="9">
+        <f>SUM(B170:P170)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="24" t="n">
+        <v>47392</v>
+      </c>
+      <c r="B171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,B$135)</f>
+        <v/>
+      </c>
+      <c r="C171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,C$135)</f>
+        <v/>
+      </c>
+      <c r="D171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,D$135)</f>
+        <v/>
+      </c>
+      <c r="E171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,E$135)</f>
+        <v/>
+      </c>
+      <c r="F171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,F$135)</f>
+        <v/>
+      </c>
+      <c r="G171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,G$135)</f>
+        <v/>
+      </c>
+      <c r="H171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,H$135)</f>
+        <v/>
+      </c>
+      <c r="I171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,I$135)</f>
+        <v/>
+      </c>
+      <c r="J171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,J$135)</f>
+        <v/>
+      </c>
+      <c r="K171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,K$135)</f>
+        <v/>
+      </c>
+      <c r="L171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,L$135)</f>
+        <v/>
+      </c>
+      <c r="M171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,M$135)</f>
+        <v/>
+      </c>
+      <c r="N171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,N$135)</f>
+        <v/>
+      </c>
+      <c r="O171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,O$135)</f>
+        <v/>
+      </c>
+      <c r="P171" s="9">
+        <f>SUMIFS($I$5:$I$89,$A$5:$A$89,$A171,$E$5:$E$89,P$135)</f>
+        <v/>
+      </c>
+      <c r="Q171" s="9">
+        <f>SUM(B171:P171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B172" s="12">
+        <f>SUM(B136:B171)</f>
+        <v/>
+      </c>
+      <c r="C172" s="12">
+        <f>SUM(C136:C171)</f>
+        <v/>
+      </c>
+      <c r="D172" s="12">
+        <f>SUM(D136:D171)</f>
+        <v/>
+      </c>
+      <c r="E172" s="12">
+        <f>SUM(E136:E171)</f>
+        <v/>
+      </c>
+      <c r="F172" s="12">
+        <f>SUM(F136:F171)</f>
+        <v/>
+      </c>
+      <c r="G172" s="12">
+        <f>SUM(G136:G171)</f>
+        <v/>
+      </c>
+      <c r="H172" s="12">
+        <f>SUM(H136:H171)</f>
+        <v/>
+      </c>
+      <c r="I172" s="12">
+        <f>SUM(I136:I171)</f>
+        <v/>
+      </c>
+      <c r="J172" s="12">
+        <f>SUM(J136:J171)</f>
+        <v/>
+      </c>
+      <c r="K172" s="12">
+        <f>SUM(K136:K171)</f>
+        <v/>
+      </c>
+      <c r="L172" s="12">
+        <f>SUM(L136:L171)</f>
+        <v/>
+      </c>
+      <c r="M172" s="12">
+        <f>SUM(M136:M171)</f>
+        <v/>
+      </c>
+      <c r="N172" s="12">
+        <f>SUM(N136:N171)</f>
+        <v/>
+      </c>
+      <c r="O172" s="12">
+        <f>SUM(O136:O171)</f>
+        <v/>
+      </c>
+      <c r="P172" s="12">
+        <f>SUM(P136:P171)</f>
+        <v/>
+      </c>
+      <c r="Q172" s="12">
+        <f>SUM(Q136:Q171)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K89"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
